--- a/output/福利厚生規程_いいかいご.xlsx
+++ b/output/福利厚生規程_いいかいご.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1184,331 +1184,341 @@
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>第16条　会社は、正社員に対し、一律月額10,000円の食事補助手当を支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="8" customHeight="1"/>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="5" t="inlineStr">
+          <t>第16条　会社は、従業員に対し、月額10,000円の食事補助手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="32" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>2　パートタイマー等の所定労働日数が少ない従業員については、出勤日数に応じて按分して支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="8" customHeight="1"/>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>（制服・作業着）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="32" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>第17条　従業員は、業務に従事するにあたり会社が指定する制服または作業着を着用しなければならない。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="32" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
+          <t>第17条　従業員は、業務に従事するにあたり会社が指定する制服または作業着を着用しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
           <t>2　制服または作業着は、原則として従業員が自ら準備するものとする。ただし、会社が特に必要と認めた場合は、会社が貸与または支給することがある。</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="8" customHeight="1"/>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>（慶弔給付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>第18条　会社は、休暇規程に定める慶弔休暇に関連して、次の給付を行う。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>1　結婚祝い金：30,000円</t>
+          <t>第18条　会社は、休暇規程に定める慶弔休暇に関連して、次の給付を行う。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>2　出産祝い金：30,000円</t>
+          <t>1　結婚祝い金：30,000円</t>
         </is>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>3　弔事：本人または家族の希望に応じ、生花を手配する。</t>
+          <t>2　出産祝い金：30,000円</t>
         </is>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
+          <t>3　弔事：本人または家族の希望に応じ、生花を手配する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
           <t>4　災害見舞金：取締役会の判断により、最大100,000円を限度として支給する。</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="8" customHeight="1"/>
-    <row r="145" ht="8" customHeight="1">
-      <c r="A145" s="7" t="inlineStr"/>
-      <c r="B145" s="8" t="n"/>
-      <c r="C145" s="8" t="n"/>
-      <c r="D145" s="8" t="n"/>
-      <c r="E145" s="8" t="n"/>
-    </row>
-    <row r="146" ht="10" customHeight="1"/>
-    <row r="147" ht="30" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
+    <row r="145" ht="8" customHeight="1"/>
+    <row r="146" ht="8" customHeight="1">
+      <c r="A146" s="7" t="inlineStr"/>
+      <c r="B146" s="8" t="n"/>
+      <c r="C146" s="8" t="n"/>
+      <c r="D146" s="8" t="n"/>
+      <c r="E146" s="8" t="n"/>
+    </row>
+    <row r="147" ht="10" customHeight="1"/>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>第7章　健康・医療支援</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>（健康診断）</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="32" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
+    <row r="150" ht="32" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>第19条　会社は、労働安全衛生法に基づき、従業員に対し年1回の健康診断を実施し、費用を会社が負担する。</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>2　夜勤に従事する従業員については、年2回実施し、費用は会社が負担する。</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="8" customHeight="1"/>
-    <row r="152" ht="8" customHeight="1">
-      <c r="A152" s="7" t="inlineStr"/>
-      <c r="B152" s="8" t="n"/>
-      <c r="C152" s="8" t="n"/>
-      <c r="D152" s="8" t="n"/>
-      <c r="E152" s="8" t="n"/>
-    </row>
-    <row r="153" ht="10" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="152" ht="8" customHeight="1"/>
+    <row r="153" ht="8" customHeight="1">
+      <c r="A153" s="7" t="inlineStr"/>
+      <c r="B153" s="8" t="n"/>
+      <c r="C153" s="8" t="n"/>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="8" t="n"/>
+    </row>
+    <row r="154" ht="10" customHeight="1"/>
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>第8章　教育研修</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>（外部研修）</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="6" t="inlineStr">
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>第20条　会社は、業務に資すると判断される外部研修について、参加費用を全額負担する。</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="8" customHeight="1"/>
-    <row r="158" ht="8" customHeight="1">
-      <c r="A158" s="7" t="inlineStr"/>
-      <c r="B158" s="8" t="n"/>
-      <c r="C158" s="8" t="n"/>
-      <c r="D158" s="8" t="n"/>
-      <c r="E158" s="8" t="n"/>
-    </row>
-    <row r="159" ht="10" customHeight="1"/>
-    <row r="160" ht="30" customHeight="1">
-      <c r="A160" s="4" t="inlineStr">
+    <row r="158" ht="8" customHeight="1"/>
+    <row r="159" ht="8" customHeight="1">
+      <c r="A159" s="7" t="inlineStr"/>
+      <c r="B159" s="8" t="n"/>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="8" t="n"/>
+    </row>
+    <row r="160" ht="10" customHeight="1"/>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
         <is>
           <t>第9章　特別休暇に関連する給付</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="5" t="inlineStr">
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>（誕生日休暇・手当）</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="6" t="inlineStr">
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>第21条　会社は、休暇規程に基づき誕生日休暇を付与するとともに、当該休暇を取得した従業員に対して誕生日手当として10,000円を支給する。</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="8" customHeight="1"/>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="5" t="inlineStr">
+    <row r="164" ht="8" customHeight="1"/>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
         <is>
           <t>（特別休暇に伴う給付）</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="32" customHeight="1">
-      <c r="A165" s="6" t="inlineStr">
+    <row r="166" ht="32" customHeight="1">
+      <c r="A166" s="6" t="inlineStr">
         <is>
           <t>第22条　会社は、休暇規程に基づき付与される特別休暇について、必要に応じて記念品、金銭その他の給付を行うことができる。内容は取締役会の決議により定める。</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="8" customHeight="1"/>
-    <row r="167" ht="8" customHeight="1">
-      <c r="A167" s="7" t="inlineStr"/>
-      <c r="B167" s="8" t="n"/>
-      <c r="C167" s="8" t="n"/>
-      <c r="D167" s="8" t="n"/>
-      <c r="E167" s="8" t="n"/>
-    </row>
-    <row r="168" ht="10" customHeight="1"/>
-    <row r="169" ht="30" customHeight="1">
-      <c r="A169" s="4" t="inlineStr">
+    <row r="167" ht="8" customHeight="1"/>
+    <row r="168" ht="8" customHeight="1">
+      <c r="A168" s="7" t="inlineStr"/>
+      <c r="B168" s="8" t="n"/>
+      <c r="C168" s="8" t="n"/>
+      <c r="D168" s="8" t="n"/>
+      <c r="E168" s="8" t="n"/>
+    </row>
+    <row r="169" ht="10" customHeight="1"/>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t>第10章　運用</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="5" t="inlineStr">
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t>（支給方法）</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="32" customHeight="1">
-      <c r="A171" s="6" t="inlineStr">
+    <row r="172" ht="32" customHeight="1">
+      <c r="A172" s="6" t="inlineStr">
         <is>
           <t>第23条　通勤手当、特別通勤手当及び各種手当は、毎月1日から末日までの1か月分を集計し、当月の給与と併せて支給する。</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="8" customHeight="1"/>
-    <row r="173" ht="20" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
+    <row r="173" ht="8" customHeight="1"/>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>（中途入社・退職時の取扱い）</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="6" t="inlineStr">
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
         <is>
           <t>第24条　月中に入社または退職した者についても、出勤日数に応じて日割り計算で支給する。</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="8" customHeight="1"/>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="5" t="inlineStr">
+    <row r="176" ht="8" customHeight="1"/>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>（休職・休暇・在宅勤務時の取扱い）</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="32" customHeight="1">
-      <c r="A177" s="6" t="inlineStr">
+    <row r="178" ht="32" customHeight="1">
+      <c r="A178" s="6" t="inlineStr">
         <is>
           <t>第25条　休職中・休暇中・休業中または在宅勤務の場合、通勤手当及び特別通勤手当は支給しない。</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="8" customHeight="1"/>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="5" t="inlineStr">
+    <row r="179" ht="8" customHeight="1"/>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t>（虚偽申請の禁止）</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="6" t="inlineStr">
+    <row r="181" ht="32" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>第26条　通勤手当、特別通勤手当、住宅手当その他各種手当の申請に虚偽が発覚した場合、会社は入社時に遡って再計算を行い、超過支給分を返還請求できるものとする。</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="8" customHeight="1"/>
-    <row r="182" ht="8" customHeight="1">
-      <c r="A182" s="7" t="inlineStr"/>
-      <c r="B182" s="8" t="n"/>
-      <c r="C182" s="8" t="n"/>
-      <c r="D182" s="8" t="n"/>
-      <c r="E182" s="8" t="n"/>
-    </row>
-    <row r="183" ht="10" customHeight="1"/>
-    <row r="184" ht="30" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
+    <row r="182" ht="8" customHeight="1"/>
+    <row r="183" ht="8" customHeight="1">
+      <c r="A183" s="7" t="inlineStr"/>
+      <c r="B183" s="8" t="n"/>
+      <c r="C183" s="8" t="n"/>
+      <c r="D183" s="8" t="n"/>
+      <c r="E183" s="8" t="n"/>
+    </row>
+    <row r="184" ht="10" customHeight="1"/>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>第11章　雑則</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="20" customHeight="1">
-      <c r="A185" s="5" t="inlineStr">
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="5" t="inlineStr">
         <is>
           <t>（周知）</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="32" customHeight="1">
-      <c r="A186" s="6" t="inlineStr">
+    <row r="187" ht="32" customHeight="1">
+      <c r="A187" s="6" t="inlineStr">
         <is>
           <t>第27条　会社は、本規程の内容を従業員に周知し、常時確認できるよう掲示またはイントラネット等で公開する。</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="8" customHeight="1"/>
-    <row r="188" ht="8" customHeight="1">
-      <c r="A188" s="7" t="inlineStr"/>
-      <c r="B188" s="8" t="n"/>
-      <c r="C188" s="8" t="n"/>
-      <c r="D188" s="8" t="n"/>
-      <c r="E188" s="8" t="n"/>
-    </row>
-    <row r="189" ht="10" customHeight="1"/>
-    <row r="190" ht="30" customHeight="1">
-      <c r="A190" s="4" t="inlineStr">
+    <row r="188" ht="8" customHeight="1"/>
+    <row r="189" ht="8" customHeight="1">
+      <c r="A189" s="7" t="inlineStr"/>
+      <c r="B189" s="8" t="n"/>
+      <c r="C189" s="8" t="n"/>
+      <c r="D189" s="8" t="n"/>
+      <c r="E189" s="8" t="n"/>
+    </row>
+    <row r="190" ht="10" customHeight="1"/>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="20" customHeight="1">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
         </is>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="6" t="inlineStr">
         <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
           <t>2　本規程は、令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="122">
+    <mergeCell ref="A166:E166"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A142:E142"/>
-    <mergeCell ref="A182:E182"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A168:E168"/>
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A89:E89"/>
@@ -1519,10 +1529,9 @@
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
     <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A179:E179"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A185:E185"/>
-    <mergeCell ref="A184:E184"/>
+    <mergeCell ref="A181:E181"/>
     <mergeCell ref="A131:E131"/>
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A43:E43"/>
@@ -1533,29 +1542,31 @@
     <mergeCell ref="A115:E115"/>
     <mergeCell ref="A155:E155"/>
     <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A173:E173"/>
     <mergeCell ref="A130:E130"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A83:E83"/>
     <mergeCell ref="A148:E148"/>
-    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A157:E157"/>
     <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A183:E183"/>
     <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A175:E175"/>
     <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A159:E159"/>
     <mergeCell ref="A97:E97"/>
     <mergeCell ref="A106:E106"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A147:E147"/>
     <mergeCell ref="A161:E161"/>
     <mergeCell ref="A170:E170"/>
     <mergeCell ref="A31:E31"/>
@@ -1565,59 +1576,56 @@
     <mergeCell ref="A73:E73"/>
     <mergeCell ref="A123:E123"/>
     <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A172:E172"/>
+    <mergeCell ref="A187:E187"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A174:E174"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="A149:E149"/>
-    <mergeCell ref="A158:E158"/>
+    <mergeCell ref="A189:E189"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A151:E151"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A160:E160"/>
     <mergeCell ref="A141:E141"/>
     <mergeCell ref="A135:E135"/>
     <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A134:E134"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A152:E152"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A167:E167"/>
-    <mergeCell ref="A176:E176"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A114:E114"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A98:E98"/>
     <mergeCell ref="A191:E191"/>
-    <mergeCell ref="A169:E169"/>
     <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A178:E178"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A153:E153"/>
     <mergeCell ref="A162:E162"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A177:E177"/>
     <mergeCell ref="A90:E90"/>
     <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A164:E164"/>
     <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A154:E154"/>
+    <mergeCell ref="A163:E163"/>
     <mergeCell ref="A101:E101"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A188:E188"/>
     <mergeCell ref="A126:E126"/>
     <mergeCell ref="A140:E140"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A180:E180"/>
-    <mergeCell ref="A190:E190"/>
     <mergeCell ref="A102:E102"/>
     <mergeCell ref="A117:E117"/>
     <mergeCell ref="A111:E111"/>
